--- a/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-3 地表的改變　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上5-3 地表的改變　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>岩石在原地被分解破碎是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>風化</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>水與氣體反應</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>侵蝕</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>外營力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>原地</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>風水冰移走岩屑是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>U型谷等</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>沙灘沙洲</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>侵蝕</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>很長時間</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>移走</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>把碎屑帶到他處是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>三角洲</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>搬運</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>侵蝕</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>運送</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>碎屑沉積下來是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>搬運</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>堆積</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>三角洲</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>沉積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>熱脹冷縮造成的風化屬？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>外營力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>物理風化</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>化學風化</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>機械</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>河口常形成什麼堆積地形？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>三角洲</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>化學風化</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>風水冰川</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>堆積</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>土壤由岩石風化加什麼？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>搬運</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>化學風化</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>有機質</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>形成</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>土壤形成需要？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>外營力</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>有機質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水與氣體反應</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>很長時間</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>緩慢</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>把侵蝕下來的物質帶往他處是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>很長時間</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>搬運</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>水與氣體反應</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>搬運</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>風化與侵蝕何者發生在原地？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>很長時間</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>搬運</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>風化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>風水冰川</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>原地</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-3 地表的改變　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上5-3 地表的改變　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>風化與侵蝕差別？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>搬運力減弱時大顆粒先沉積</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>河流入海流速驟減堆積泥沙</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>大量降雨侵蝕搬運鬆散物質</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>風化原地、侵蝕移走</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>能造成侵蝕的營力有？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>U型谷等</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>沙灘沙洲</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>風水冰川</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>很長時間</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>多種</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>化學風化常靠什麼進行？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>水與氣體反應</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>有機質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>U型谷等</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>侵蝕</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>化學</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>堆積物顆粒常依什麼排列？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>化學風化</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>堆積</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>大小分選</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分選</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>冰川侵蝕形成的地形？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>侵蝕</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>U型谷等</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>物理風化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>化學風化</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>冰蝕</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>海浪堆積形成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>沙灘沙洲</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>U型谷等</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>三角洲</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大小分選</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>海積</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>風化是內營力還外營力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>外營力</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>堆積</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>侵蝕</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>風水冰川</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>地表</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>搬運能力越強能帶動顆粒？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>風水冰川</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>沙灘沙洲</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>物理風化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>河流入海口堆積常形成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>有機質</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>外營力</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>三角洲</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>很長時間</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>堆積</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>岩石因水氣反應而分解屬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>風化</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>有機質</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>化學風化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>化學</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-3 地表的改變　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上5-3 地表的改變　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明岩石變成土壤的完整過程？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>風化破碎岩石再與有機質長期作用成土</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>前者改變外形、後者改變成分</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>風化原地分解、侵蝕移走物質</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>河流入海流速驟減堆積泥沙</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>過程</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何堆積物會有分選現象？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>外營力不斷風化侵蝕堆積</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>風化原地、侵蝕移走</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>搬運力減弱時大顆粒先沉積</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>風化原地分解、侵蝕移走物質</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分選</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>比較物理風化與化學風化？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>大量降雨侵蝕搬運鬆散物質</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>風化原地分解、侵蝕移走物質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>失去植被保護侵蝕加劇</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>前者改變外形、後者改變成分</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>土石流形成與侵蝕搬運關係？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>大量降雨侵蝕搬運鬆散物質</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>風化原地、侵蝕移走</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>搬運力減弱時大顆粒先沉積</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>失去植被保護侵蝕加劇</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>災害</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>三角洲如何形成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>破壞植被使侵蝕加劇</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>搬運力減弱時大顆粒先沉積</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>河流入海流速驟減堆積泥沙</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>風化原地、侵蝕移走</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>堆積</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>過度開發如何加速土壤流失？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>前者改變外形、後者改變成分</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>大量降雨侵蝕搬運鬆散物質</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>破壞植被使侵蝕加劇</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>風化原地、侵蝕移走</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>人為</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何說地表持續在變？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>搬運力減弱時大顆粒先沉積</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>前者改變外形、後者改變成分</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>冰川成U谷、河流成V谷</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>外營力不斷風化侵蝕堆積</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>動態</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>冰川與河流侵蝕地形差異？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>冰川成U谷、河流成V谷</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>破壞植被使侵蝕加劇</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>風化原地分解、侵蝕移走物質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>風化原地、侵蝕移走</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>比較風化與侵蝕的差別？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>失去植被保護侵蝕加劇</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>河流入海流速驟減堆積泥沙</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>冰川成U谷、河流成V谷</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>風化原地分解、侵蝕移走物質</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>過度砍伐森林為何加速土壤流失？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>冰川成U谷、河流成V谷</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>搬運力減弱時大顆粒先沉積</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>大量降雨侵蝕搬運鬆散物質</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>失去植被保護侵蝕加劇</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>人為</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>原地</t>
+          <t>原地：岩石不用被搬走,就在原本的地方慢慢裂開破碎,叫做風化</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>移走</t>
+          <t>移走：風、水、冰川這些力量把已經破碎的岩屑從原地帶走,叫做侵蝕</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>運送</t>
+          <t>運送：河流、風等把侵蝕下來的碎屑一路帶到別的地方,就是搬運</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>沉積</t>
+          <t>沉積：被搬運的碎屑物質失去動力後,慢慢沉澱下來,就是堆積</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>機械</t>
+          <t>機械：白天熱晚上冷,岩石反覆膨脹收縮而裂開,屬於物理(機械)風化</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>堆積</t>
+          <t>堆積：河水流到出海口速度變慢,帶來的泥沙堆積形成扇形的三角洲</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>形成</t>
+          <t>形成：岩石經風化變成細碎顆粒,再混入動植物腐爛的有機質才形成土壤</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>緩慢：岩石要風化再和有機質結合成土壤,是一個非常緩慢漫長的過程</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>搬運</t>
+          <t>搬運：風化侵蝕產生的碎屑物質,被水流、風或冰川等外力帶到別的地方,這個過程叫做搬運</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>原地</t>
+          <t>原地：風化是岩石在原地受日曬雨淋等作用逐漸崩解破碎,不涉及物質的移動;侵蝕則會把碎屑帶離原地</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：風化是岩石在原地被分解,侵蝕則是外力把破碎物質從原地帶走,兩者關鍵差別在有沒有移動</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>多種</t>
+          <t>多種：風、河水、海浪、冰川這些自然力量都能把地表物質侵蝕帶走</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>化學</t>
+          <t>化學：水或空氣中的氣體和岩石礦物發生化學反應,使岩石成分改變而分解</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分選</t>
+          <t>分選：搬運力量減弱時,較重較大的顆粒先沉下來,較輕較小的顆粒沉得比較後面</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>冰蝕</t>
+          <t>冰蝕：厚重的冰川緩慢移動刮蝕山谷兩側,常常會刻出兩側較陡的U字型山谷</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>海積</t>
+          <t>海積：海浪把泥沙一波波推到岸邊堆積,長時間累積就形成沙灘或沙洲</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>地表</t>
+          <t>地表：風化是來自地球表面外在環境的作用力,所以屬於外營力</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：搬運的力量(例如水流速度)越強,就有足夠能量帶動更大更重的顆粒移動</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>堆積</t>
+          <t>堆積：河流流速在出海口附近變慢,原本搬運的泥沙大量堆積下來,日積月累就形成三角洲地形</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>化學</t>
+          <t>化學：岩石礦物與水、空氣中的物質發生化學反應而分解、變質,這種風化方式稱為化學風化</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>過程</t>
+          <t>過程：岩石先經過長時間風化裂成細小顆粒,再和動植物遺骸分解的有機質混合,經過長久累積才慢慢形成土壤</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分選</t>
+          <t>分選：水流或風的搬運力量逐漸變弱時,重的大顆粒會先失去動力沉下來,輕的小顆粒能繼續被帶得更遠才沉積</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：物理風化只是把岩石弄裂變小塊但成分不變,化學風化則是讓岩石礦物發生反應,連本身的化學成分都改變了</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>災害</t>
+          <t>災害：大雨時強大的水流侵蝕山坡上鬆散的土石,並把它們快速搬運沖下山,就形成危險的土石流</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>堆積</t>
+          <t>堆積：河水流進海洋時速度突然變慢,原本被帶著走的泥沙沒有力量繼續前進,就在出海口大量堆積形成三角洲</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>人為</t>
+          <t>人為：砍伐森林開發土地後,失去植物根系抓住泥土的保護,雨水更容易把表土沖刷侵蝕流失</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>動態</t>
+          <t>動態：風化、侵蝕、搬運、堆積這些外營力作用一直在進行,地表的樣貌因此持續緩慢地改變著</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：冰川又厚又寬,刮蝕出兩側陡峭底部平坦的U字型山谷;河流集中在窄溝裡向下切,刻出尖底的V字型山谷</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：風化是岩石在原地被破壞分解,不會移動位置;侵蝕則是外力(水、風等)把已經破碎的物質帶離原地,兩者常常接續發生</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>人為</t>
+          <t>人為：植物的根系能固定土壤、減緩雨水沖刷,森林被砍伐後土壤失去保護,雨水更容易把表土沖走,加速侵蝕流失</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>水與氣體反應</t>
+          <t>搬運</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>侵蝕</t>
+          <t>三角洲</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>外營力</t>
+          <t>大小分選</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -723,22 +723,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>風化</t>
+          <t>搬運</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>有機質</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>物理風化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>外營力</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>物理風化</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>化學風化</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>很長時間</t>
+          <t>三角洲</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>風水冰川</t>
+          <t>侵蝕</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>很長時間</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>風化</t>
+          <t>風水冰川</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>有機質</t>
+          <t>U型谷等</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
